--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCP.xlsx
@@ -422,23 +422,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>24.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCP_L._REILLY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCP_D._VENTURA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -484,11 +751,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -546,34 +813,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>F. Amarante</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
         </is>
       </c>
     </row>
@@ -632,16 +933,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.3</v>
+        <v>77.3</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.6</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="3">
@@ -651,16 +952,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>98.40000000000001</v>
+        <v>102.9</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>-12</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +971,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="5">
@@ -689,16 +990,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-14.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>-14.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +1009,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.2</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="7">
@@ -727,13 +1028,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C7" t="n">
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
@@ -749,13 +1050,13 @@
         <v>0.3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -765,16 +1066,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="10">
@@ -784,7 +1085,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
@@ -793,7 +1094,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -809,10 +1110,10 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -865,7 +1166,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Below-average assist profile; more possessions end through direct creation than collective flow.</t>
+          <t>Ball movement is close to league average; they can share it but are not purely pass-first.</t>
         </is>
       </c>
     </row>
@@ -877,7 +1178,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
         </is>
       </c>
     </row>
@@ -901,7 +1202,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
+          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -967,7 +1268,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Win the first action: they do not consistently hurt teams with second-chance volume, so clean first stops carry value.</t>
+          <t>Know the first reference: Liam Reilly is a primary scorer, and the plan should start with taking away his comfort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Closeout discipline matters: Liam Reilly, G. Kalscheur are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -982,7 +1295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1004,48 +1317,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from F. Amarante and G. Kalscheur; contest, but do not over-help into secondary advantages.</t>
+          <t>The main offensive references are F. Amarante and Liam Reilly; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
+          <t>Priority closeouts start with Liam Reilly, G. Kalscheur, and F. Amarante; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially G. Kalscheur and 0; force them away from preferred areas.</t>
+          <t>Some perimeter volume comes from F. Amarante and D. Ventura; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Several players have clear comfort zones, especially G. Kalscheur, Liam Reilly, and J. Davis; force them away from preferred areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Do not lose Liam Reilly and G. Kalscheur in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1060,23 +1409,202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>inside scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCP_LIAM_REILLY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>primary scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCP_D._VENTURA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1185,41 +1713,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -1231,7 +1759,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1245,23 +1773,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1277,41 +1805,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SCP_D._VENTURA</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1328,36 +1856,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SCP_J._EMBALO</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J. Embalo</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1369,110 +1897,140 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SCP_D._VENTURA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>21</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>19.0%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>31.8%</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>18</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SCP_J._EMBALO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>J. Embalo</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>11</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SCP_J._GOMES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>J. Gomes</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1490,23 +2048,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -1526,42 +2084,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SCP_G._KALSCHEUR</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>G. Kalscheur</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -1570,42 +2120,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>19.8%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SCP_0</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -1614,23 +2156,323 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>13</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SCP_G._KALSCHEUR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SCP_LIAM_REILLY</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SCP_J._DAVIS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>J. Davis</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SCP_D._VENTURA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SCP_F._AMARANTE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>6</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>33.3%</t>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SCP_T._BASKIN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>T. Baskin</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCP.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -515,36 +515,36 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -556,52 +556,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_L._REILLY</t>
+          <t>SCP_D._VENTURA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -619,31 +619,31 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,52 +660,312 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_D._VENTURA</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCP_J._EMBALO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Embalo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCP_L._REILLY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCP_T._BASKIN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T. Baskin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>16.2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SCP_J._FERNANDES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>J. Fernandes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SCP_A._CRUZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A. Cruz</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.0</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
     </row>
@@ -933,16 +1193,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.4</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="3">
@@ -952,16 +1212,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102.9</v>
+        <v>105.9</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
@@ -971,16 +1231,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93.09999999999999</v>
+        <v>102.3</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>-13.6</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="5">
@@ -990,16 +1250,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>10.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="6">
@@ -1009,16 +1269,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="7">
@@ -1034,7 +1294,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
@@ -1053,10 +1313,10 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1066,16 +1326,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.5</v>
+        <v>20.7</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -1091,7 +1351,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0.1</v>
@@ -1110,7 +1370,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1178,7 +1438,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+          <t>Second-chance threat; the first stop is not enough against this team.</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1462,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
+          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1268,7 +1528,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Know the first reference: Liam Reilly is a primary scorer, and the plan should start with taking away his comfort.</t>
+          <t>Finish possessions: the first stop is not enough against this team because the offensive glass is a real source of extra points.</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1540,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Closeout discipline matters: Liam Reilly, G. Kalscheur are the first perimeter names you cannot lose in help situations.</t>
+          <t>Know the first reference: Liam Reilly is a primary scorer, and the plan should start with taking away his comfort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Closeout discipline matters: Liam Reilly, F. Amarante are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1594,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The main offensive references are F. Amarante and Liam Reilly; load the scouting plan into those names first.</t>
+          <t>The main offensive references are F. Amarante and D. Ventura; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1606,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with Liam Reilly, G. Kalscheur, and F. Amarante; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with Liam Reilly, F. Amarante, and G. Kalscheur; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1618,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from F. Amarante and D. Ventura; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from D. Ventura and J. Embalo; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1642,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially G. Kalscheur, Liam Reilly, and J. Davis; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially Liam Reilly, J. Davis, and G. Kalscheur; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1654,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+          <t>Second-chance threat; the first stop is not enough against this team.</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1666,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Do not lose Liam Reilly and G. Kalscheur in help-and-recover situations.</t>
+          <t>Do not lose Liam Reilly and F. Amarante in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1476,17 +1748,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.4</v>
+        <v>25.9</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5</v>
+        <v>11.3</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1503,26 +1775,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_D._VENTURA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.3</v>
+        <v>23.4</v>
       </c>
       <c r="D3" t="n">
-        <v>19.5</v>
+        <v>7.7</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1532,7 +1804,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>primary scorer</t>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1548,17 +1820,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.2</v>
+        <v>22.4</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1568,43 +1840,111 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_D._VENTURA</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.2</v>
+        <v>19.2</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCP_J._EMBALO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Embalo</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>14.3%</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCP_LIAM_REILLY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>18</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>primary scorer</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1727,20 +2067,20 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H2" t="n">
         <v>1.1</v>
@@ -1764,36 +2104,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1810,36 +2150,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
         <v>0.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1851,17 +2191,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_D._VENTURA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1869,23 +2209,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1911,23 +2251,23 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1957,27 +2297,27 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1994,16 +2334,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SCP_J._GOMES</t>
+          <t>SCP_G._TEIXEIRA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>J. Gomes</t>
+          <t>G. Teixeira</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2016,14 +2356,14 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -2035,38 +2375,48 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>36</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>27.5%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SCP_J._GOMES</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>J. Gomes</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2084,23 +2434,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.1%</t>
         </is>
       </c>
     </row>
@@ -2120,23 +2470,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -2156,23 +2506,23 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>19.9%</t>
         </is>
       </c>
     </row>
@@ -2196,38 +2546,30 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SCP_G._KALSCHEUR</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>G. Kalscheur</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -2236,23 +2578,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2626,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2296,7 +2638,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
     </row>
@@ -2328,19 +2670,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2694,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SCP_D._VENTURA</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2372,19 +2714,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2738,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_D._VENTURA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2412,23 +2754,23 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2782,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2456,23 +2798,155 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>31.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SCP_T._BASKIN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>T. Baskin</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SCP_A._CRUZ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A. Cruz</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SCP_B._CARTER</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B. Carter</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>5</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>45.5%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCP.xlsx
@@ -515,36 +515,36 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -567,26 +567,26 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -608,312 +608,312 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_L._REILLY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCP_J._EMBALO</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Embalo</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_L._REILLY</t>
+          <t>SCP_J._EMBALO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>J. Embalo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCP_T._BASKIN</t>
+          <t>SCP_J._FERNANDES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>J. Fernandes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SCP_J._FERNANDES</t>
+          <t>SCP_T._BASKIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -980,24 +980,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>F. Amarante | Liam Reilly</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>D. Ventura | G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>D. Ventura | G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21.7</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1233,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
     </row>
@@ -1193,10 +1309,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
@@ -1212,16 +1328,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105.9</v>
+        <v>101.8</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="4">
@@ -1231,16 +1347,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>102.3</v>
+        <v>98.8</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.6</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="5">
@@ -1250,16 +1366,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -1269,16 +1385,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="7">
@@ -1294,10 +1410,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1313,7 +1429,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1326,16 +1442,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.7</v>
+        <v>19.2</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>-0</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="10">
@@ -1345,7 +1461,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
@@ -1370,7 +1486,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1450,7 +1566,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
+          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1578,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
+          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1590,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Perimeter volume is close to league average; shot mix alone does not define them.</t>
+          <t>Above-average three-point volume; spacing discipline and clean closeouts matter.</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1656,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Know the first reference: Liam Reilly is a primary scorer, and the plan should start with taking away his comfort.</t>
+          <t>Stay connected to spacing: their perimeter volume can bend the floor if your help and recovery are sloppy.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1668,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Closeout discipline matters: Liam Reilly, F. Amarante are the first perimeter names you cannot lose in help situations.</t>
+          <t>Know the first reference: Liam Reilly is a spot-up shooter, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1606,7 +1722,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with Liam Reilly, F. Amarante, and G. Kalscheur; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with Liam Reilly, G. Kalscheur, and F. Amarante; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1746,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
@@ -1642,19 +1758,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially Liam Reilly, J. Davis, and G. Kalscheur; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially J. Davis, Liam Reilly, and G. Kalscheur; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Defensive Emphasis</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Second-chance threat; the first stop is not enough against this team.</t>
+          <t>Recognize the main duo/trio combinations: F. Amarante | Liam Reilly and D. Ventura | G. Kalscheur.</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1782,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Do not lose Liam Reilly and F. Amarante in help-and-recover situations.</t>
+          <t>Second-chance threat; the first stop is not enough against this team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Do not lose Liam Reilly and G. Kalscheur in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1819,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1748,17 +1876,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1768,7 +1896,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>inside scorer</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
@@ -1784,17 +1912,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.4</v>
+        <v>25.4</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1804,33 +1932,33 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>10.7</v>
+        <v>15.2</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1840,101 +1968,101 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>bench spacer</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.2</v>
+        <v>23.1</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCP_J._EMBALO</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Embalo</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.2</v>
+        <v>19.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>11.2</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_J._EMBALO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>J. Embalo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24.3</v>
+        <v>19.6</v>
       </c>
       <c r="D7" t="n">
-        <v>19.5</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1944,7 +2072,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>primary scorer</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -2067,23 +2195,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2104,36 +2232,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SCP_F._AMARANTE</t>
+          <t>SCP_G._KALSCHEUR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -2150,36 +2278,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SCP_G._KALSCHEUR</t>
+          <t>SCP_F._AMARANTE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -2205,23 +2333,23 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2251,23 +2379,23 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2297,23 +2425,23 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2434,23 +2562,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>30.1%</t>
         </is>
       </c>
     </row>
@@ -2470,23 +2598,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.3%</t>
         </is>
       </c>
     </row>
@@ -2510,19 +2638,19 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -2542,23 +2670,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.8%</t>
         </is>
       </c>
     </row>
@@ -2578,23 +2706,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2734,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SCP_LIAM_REILLY</t>
+          <t>SCP_J._DAVIS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liam Reilly</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2622,23 +2750,23 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2778,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SCP_J._DAVIS</t>
+          <t>SCP_LIAM_REILLY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2666,23 +2794,23 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -2714,19 +2842,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
     </row>
@@ -2758,19 +2886,19 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -2802,19 +2930,19 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2998,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SCP_A._CRUZ</t>
+          <t>SCP_B._CARTER</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>B. Carter</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -2890,15 +3018,15 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2914,12 +3042,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SCP_B._CARTER</t>
+          <t>SCP_A._CRUZ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B. Carter</t>
+          <t>A. Cruz</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2930,23 +3058,23 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
